--- a/resampling/input/accessibility_reports_generated/Malteser_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/Malteser_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q37" headerRowCount="1">
-  <autoFilter ref="A1:Q37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q62" headerRowCount="1">
+  <autoFilter ref="A1:Q62"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O68" headerRowCount="1">
-  <autoFilter ref="A1:O68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O61" headerRowCount="1">
+  <autoFilter ref="A1:O61"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 36 wards, 67 clusters</t>
+          <t>Assigned to you: 61 wards, 60 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guma</t>
+          <t>Gwer West</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -882,25 +882,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Agan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -923,25 +931,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Modern Market</t>
+          <t>Akpanaja</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Agatu; Gwer West</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -964,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Ankpa / Wadata</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -976,13 +992,13 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1005,7 +1021,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mbalagh</t>
+          <t>Central / South Mission</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1017,13 +1033,13 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1064,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1087,25 +1103,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Agan</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1128,7 +1152,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wailomayo</t>
+          <t>Mbalagh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1140,13 +1164,13 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1169,25 +1193,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ankpa / Wadata</t>
+          <t>Mbawa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1210,25 +1242,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North Bank 2</t>
+          <t>Mbayer / Yandev</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1251,25 +1291,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central / South Mission</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1282,17 +1330,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Makurdi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>North Bank 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1304,13 +1352,13 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1323,17 +1371,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Makurdi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Birchi</t>
+          <t>North Bank 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1345,13 +1393,13 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1364,35 +1412,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Makurdi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rawayau A</t>
+          <t>Nyamshi / Mbanyamshi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1405,35 +1461,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Makurdi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Barkiya</t>
+          <t>Tyoughatee / Ijaha</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1446,17 +1510,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Makurdi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tsauri B</t>
+          <t>Wailomayo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1468,13 +1532,13 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1497,25 +1561,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wurma A</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Batagarawa; Batsari</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1538,7 +1610,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tsauri A</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1553,10 +1625,10 @@
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1579,7 +1651,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wurma B</t>
+          <t>Kurfi B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1590,7 +1662,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Safana</t>
+          <t>Batsari; Safana</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1599,13 +1671,13 @@
         </is>
       </c>
       <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>3</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>9</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1628,7 +1700,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kurfi B</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1639,7 +1711,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Batsari</t>
+          <t>Dutsin-Ma</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1651,10 +1723,10 @@
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1677,7 +1749,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rawayau B</t>
+          <t>Tsauri B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1688,7 +1760,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dutsin-Ma</t>
+          <t>Batsari</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1697,7 +1769,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1726,7 +1798,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Banye</t>
+          <t>Tsanni</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1737,7 +1809,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Charanchi</t>
+          <t>Batagarawa; Rimi</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1775,7 +1847,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dabawa</t>
+          <t>Abadau Kagara</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1786,7 +1858,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dutsin-Ma</t>
+          <t>Batsari</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1795,13 +1867,13 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1824,25 +1896,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tsanni</t>
+          <t>Banye</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1860,38 +1940,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Barkiya</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Mani</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1909,12 +1981,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Dabaibayawa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1925,7 +1997,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Batagarawa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1934,13 +2006,13 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1958,30 +2030,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Majigiri</t>
+          <t>Dabawa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dutsin-Ma; Safana</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1999,30 +2079,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Karau</t>
+          <t>Dan Alhaji Yangayya</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Batagarawa; Batsari; Jibia</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2040,30 +2128,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Doguru A</t>
+          <t>Ganuwa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2081,30 +2177,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gana Jigawa</t>
+          <t>Karare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Batsari; Safana</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2122,30 +2226,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tamilo B</t>
+          <t>Karofi A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dutsin-Ma</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2163,30 +2275,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sonkaya</t>
+          <t>Rawayau A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Charanchi; Dutsin-Ma</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2204,30 +2324,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tamilo A</t>
+          <t>Rawayau B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dutsin-Ma</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2245,12 +2373,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bamle</t>
+          <t>Shema</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2261,7 +2389,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Dutsin-Ma</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2270,13 +2398,13 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2294,12 +2422,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ba'awa</t>
+          <t>Tsaskiya</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2310,7 +2438,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaita</t>
+          <t>Dutsin-Ma; Safana</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2319,13 +2447,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2343,30 +2471,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Doguru B</t>
+          <t>Wurma A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dutsin-Ma; Safana</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2376,23 +2512,1232 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kurfi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wurma B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Safana</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kurfi</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Yargamji</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Batagarawa; Charanchi; Rimi</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kurfi</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Zakka A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Batsari; Safana</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="10" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Karau</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dutsi</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>25</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gana Jigawa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mani</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="10" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tamilo A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mani</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="10" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sonkaya</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dutsi; Mai'adua</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="10" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bamle</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mai'adua</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="10" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gallu</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mai'adua</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" s="10" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Doguru A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" s="10" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Majigiri</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kaita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" s="10" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dutsi; Mani</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" s="10" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tamilo B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kaita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" s="10" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ba'awa</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kaita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" s="10" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dankaba</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kaita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" s="10" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dankama</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kaita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="10" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Danyashe</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dutsi; Mai'adua</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="10" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Doguru B</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="10" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gafiya</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kaita; Mani; Rimi</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="10" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Hamcheta</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mani</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="10" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Muduru</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kaita; Mani; Rimi</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="10" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Natsalle</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mai'adua</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sirika A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dutsi</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="10" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tsagem Takusheyi</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mani; Rimi</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="10" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Yamel B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dutsi; Mani</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="10" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2408,7 +3753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2567,7 +3912,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2577,22 +3922,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>idp_NG007013_12</t>
+          <t>idp_NG007013_14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>In-camp</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -2616,7 +3961,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Agan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2626,7 +3971,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>idp_NG007013_14</t>
+          <t>idp_NG007013_16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2665,7 +4010,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2675,7 +4020,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>idp_NG007013_15</t>
+          <t>idp_NG007013_17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2714,7 +4059,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Agan</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2724,7 +4069,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>idp_NG007013_16</t>
+          <t>idp_NG007013_2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2763,7 +4108,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Mbalagh</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2773,7 +4118,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>idp_NG007013_17</t>
+          <t>idp_NG007013_3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2812,7 +4157,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Modern Market</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2822,22 +4167,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>idp_NG007013_2</t>
+          <t>idp_NG007013_5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>In-host</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2871,7 +4216,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>idp_NG007013_3</t>
+          <t>idp_NG007013_supp1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2910,24 +4255,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>idp_NG007013_4</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>6</t>
@@ -2959,32 +4300,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Wailomayo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>idp_NG007013_5</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>In-camp</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -3008,32 +4345,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>idp_NG007013_8</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_14</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -3057,7 +4390,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Modern Market</t>
+          <t>North Bank 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3067,7 +4400,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_1</t>
+          <t>non_idp_NG007013_15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3112,18 +4445,18 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_10</t>
+          <t>non_idp_NG007013_16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -3147,7 +4480,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3157,18 +4490,18 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_12</t>
+          <t>non_idp_NG007013_17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3192,7 +4525,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3202,7 +4535,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_14</t>
+          <t>non_idp_NG007013_2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -3237,7 +4570,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3247,7 +4580,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_15</t>
+          <t>non_idp_NG007013_3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -3282,7 +4615,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3292,7 +4625,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_16</t>
+          <t>non_idp_NG007013_4</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -3337,18 +4670,18 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_17</t>
+          <t>non_idp_NG007013_6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3372,7 +4705,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ankpa / Wadata</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3382,7 +4715,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_2</t>
+          <t>non_idp_NG007013_9</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3417,7 +4750,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Mbayer / Yandev</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3427,7 +4760,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_3</t>
+          <t>non_idp_NG007013_supp1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3462,7 +4795,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Wailomayo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3472,7 +4805,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_4</t>
+          <t>non_idp_NG007013_supp2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -3497,30 +4830,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Benue</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Makurdi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_5</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>idp_NG021022_1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>6</t>
@@ -3542,38 +4879,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Benue</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Makurdi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Clerk / Market</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_6</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>idp_NG021022_12</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3587,38 +4928,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Benue</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Makurdi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Barkiya</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_9</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>idp_NG021022_13</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3642,7 +4987,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Rawayau A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3652,7 +4997,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idp_NG021022_1</t>
+          <t>idp_NG021022_15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3662,12 +5007,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3701,7 +5046,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG021022_12</t>
+          <t>idp_NG021022_2</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3711,12 +5056,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3740,7 +5085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barkiya</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3750,7 +5095,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>idp_NG021022_13</t>
+          <t>idp_NG021022_7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3760,12 +5105,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3789,32 +5134,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rawayau A</t>
+          <t>Kurfi B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>idp_NG021022_15</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3838,32 +5179,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Tsauri B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>idp_NG021022_2</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_10</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3892,27 +5229,23 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>idp_NG021022_7</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_11</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3936,7 +5269,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kurfi B</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3946,7 +5279,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_1</t>
+          <t>non_idp_NG021022_12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -3981,7 +5314,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tsauri B</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3991,7 +5324,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_10</t>
+          <t>non_idp_NG021022_13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -4026,7 +5359,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Birchi</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4036,7 +5369,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_11</t>
+          <t>non_idp_NG021022_14</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -4071,7 +5404,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Barkiya</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4081,7 +5414,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_12</t>
+          <t>non_idp_NG021022_15</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -4116,7 +5449,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Birchi</t>
+          <t>Rawayau B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4126,7 +5459,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_13</t>
+          <t>non_idp_NG021022_16</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -4161,7 +5494,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tsauri A</t>
+          <t>Tsauri B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4171,7 +5504,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_14</t>
+          <t>non_idp_NG021022_3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -4206,7 +5539,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Barkiya</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4216,7 +5549,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_15</t>
+          <t>non_idp_NG021022_5</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -4251,7 +5584,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rawayau A</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4261,7 +5594,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_16</t>
+          <t>non_idp_NG021022_7</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -4296,7 +5629,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rawayau A</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4306,7 +5639,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_17</t>
+          <t>non_idp_NG021022_9</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -4341,7 +5674,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wurma B</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4351,7 +5684,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_2</t>
+          <t>non_idp_NG021022_supp1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -4386,7 +5719,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tsauri B</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4396,7 +5729,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_3</t>
+          <t>non_idp_NG021022_supp2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -4431,7 +5764,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wurma B</t>
+          <t>Kurfi B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4441,7 +5774,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_4</t>
+          <t>non_idp_NG021022_supp3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -4471,25 +5804,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tsauri B</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_5</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>idp_NG021027_4</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>6</t>
@@ -4516,33 +5853,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wurma A</t>
+          <t>Karau</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_6</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>idp_NG021027_supp1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4561,12 +5902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Tamilo A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4576,7 +5917,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_7</t>
+          <t>non_idp_NG021027_1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -4606,12 +5947,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wurma A</t>
+          <t>Doguru A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4621,7 +5962,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_8</t>
+          <t>non_idp_NG021027_10</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -4651,12 +5992,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Karau</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4666,7 +6007,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_9</t>
+          <t>non_idp_NG021027_11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -4701,32 +6042,28 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Majigiri</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>idp_NG021027_1</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_12</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -4750,24 +6087,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Doguru A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>idp_NG021027_4</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_13</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>6</t>
@@ -4799,32 +6132,28 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Karau</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>idp_NG021027_5</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_14</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -4848,32 +6177,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Karau</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>idp_NG021027_8</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_15</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -4897,7 +6222,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tamilo A</t>
+          <t>Gallu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4907,7 +6232,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_1</t>
+          <t>non_idp_NG021027_16</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -4942,7 +6267,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Doguru A</t>
+          <t>Sonkaya</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4952,7 +6277,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_10</t>
+          <t>non_idp_NG021027_17</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -4987,7 +6312,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Karau</t>
+          <t>Majigiri</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4997,7 +6322,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_11</t>
+          <t>non_idp_NG021027_2</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -5032,7 +6357,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Tamilo B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5042,7 +6367,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_12</t>
+          <t>non_idp_NG021027_3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -5077,7 +6402,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Doguru A</t>
+          <t>Gana Jigawa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5087,7 +6412,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_13</t>
+          <t>non_idp_NG021027_4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -5122,7 +6447,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Karau</t>
+          <t>Bamle</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5132,7 +6457,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_14</t>
+          <t>non_idp_NG021027_5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -5167,7 +6492,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Karau</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5177,18 +6502,18 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_15</t>
+          <t>non_idp_NG021027_6</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -5212,7 +6537,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Tamilo A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5222,7 +6547,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_16</t>
+          <t>non_idp_NG021027_8</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -5257,7 +6582,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sonkaya</t>
+          <t>Gana Jigawa</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5267,7 +6592,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_17</t>
+          <t>non_idp_NG021027_9</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -5289,338 +6614,23 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Majigiri</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>non_idp_NG021027_2</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Tamilo B</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>non_idp_NG021027_3</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Gana Jigawa</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>non_idp_NG021027_4</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Bamle</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>non_idp_NG021027_5</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>non_idp_NG021027_6</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Tamilo B</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>non_idp_NG021027_8</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Katsina</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Gana Jigawa</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>non_idp_NG021027_9</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="M2:M61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5886,13 +6896,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ACB795F-0DEF-432F-83E8-C28008CCED15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1A1AD6-89D0-4B66-BDB6-2DDACA1BC08F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C43D175F-1AFB-43D0-8476-F7D7B3A715D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51B8C579-361F-4594-BFA2-22465B78F6B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E384285-AC22-46FD-9F25-E702B2E0D305}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8F28A7-6F10-48F3-8C3F-1C4B9B8AF580}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/Malteser_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/Malteser_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O61" headerRowCount="1">
-  <autoFilter ref="A1:O61"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P64" headerRowCount="1">
+  <autoFilter ref="A1:P64"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 61 wards, 60 clusters</t>
+          <t>Assigned to you: 61 wards, 63 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -833,33 +844,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>North Bank 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Gwer West</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -882,7 +885,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Agan</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -893,7 +896,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guma</t>
+          <t>Gwer West</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -902,13 +905,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -931,7 +934,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Akpanaja</t>
+          <t>Agan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -942,7 +945,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Agatu; Gwer West</t>
+          <t>Guma</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -954,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -980,19 +983,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ankpa / Wadata</t>
+          <t>Akpanaja</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Agatu; Gwer West</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1021,7 +1032,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Central / South Mission</t>
+          <t>Ankpa / Wadata</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1062,7 +1073,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Clerk / Market</t>
+          <t>Central / South Mission</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1074,7 +1085,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1103,30 +1114,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Clerk / Market</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Guma</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1152,22 +1155,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mbalagh</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1193,30 +1204,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mbawa</t>
+          <t>Mbalagh</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Guma</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1242,7 +1245,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mbayer / Yandev</t>
+          <t>Mbawa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1262,7 +1265,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1291,7 +1294,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Modern Market</t>
+          <t>Mbayer / Yandev</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1302,7 +1305,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gwer West</t>
+          <t>Guma</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1311,10 +1314,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1340,22 +1343,30 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North Bank 1</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gwer West</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1381,7 +1392,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>North Bank 2</t>
+          <t>North Bank 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1393,7 +1404,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1561,33 +1572,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tsauri A</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Batagarawa; Batsari</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1610,25 +1613,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Batagarawa; Batsari</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1651,7 +1662,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kurfi B</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1662,7 +1673,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Batsari; Safana</t>
+          <t>Dutsin-Ma</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1674,10 +1685,10 @@
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1700,7 +1711,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Birchi</t>
+          <t>Kurfi B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1711,7 +1722,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dutsin-Ma</t>
+          <t>Batsari; Safana</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1723,10 +1734,10 @@
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -3737,7 +3748,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3753,7 +3764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3761,16 +3772,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3801,50 +3813,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -3878,26 +3895,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3927,26 +3949,31 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3976,26 +4003,31 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4025,26 +4057,31 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4074,26 +4111,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4123,26 +4165,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4172,26 +4219,31 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>In-camp</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4221,26 +4273,31 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4255,23 +4312,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modern Market</t>
+          <t>North Bank 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>idp_NG007013_supp2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4279,13 +4340,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4300,7 +4366,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wailomayo</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4310,27 +4376,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_10</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4345,7 +4416,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Wailomayo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4355,27 +4426,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_14</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_10</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4390,7 +4466,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North Bank 2</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4400,27 +4476,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_15</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_14</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4435,7 +4516,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>North Bank 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4445,27 +4526,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_16</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_15</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4490,27 +4576,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_17</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_16</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4525,7 +4616,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Modern Market</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4535,27 +4626,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_2</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_17</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4570,7 +4666,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4580,27 +4676,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_3</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4615,7 +4716,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Modern Market</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4625,27 +4726,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_4</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4660,7 +4766,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fiidi</t>
+          <t>Modern Market</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4670,27 +4776,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_6</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_4</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4705,7 +4816,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Fiidi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4715,27 +4826,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_9</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_6</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4750,7 +4866,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mbayer / Yandev</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4760,27 +4876,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_supp1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_9</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4795,7 +4916,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wailomayo</t>
+          <t>Mbayer / Yandev</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4805,76 +4926,82 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG007013_supp2</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007013_supp1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kurfi</t>
+          <t>Makurdi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Wailomayo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>idp_NG021022_1</t>
+          <t>non_idp_NG007013_supp2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4899,31 +5026,36 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>idp_NG021022_12</t>
+          <t>idp_NG021022_1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4938,7 +5070,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Barkiya</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4948,31 +5080,36 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>idp_NG021022_13</t>
+          <t>idp_NG021022_12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4987,7 +5124,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rawayau A</t>
+          <t>Barkiya</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4997,31 +5134,36 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idp_NG021022_15</t>
+          <t>idp_NG021022_13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5036,7 +5178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Rawayau A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5046,31 +5188,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG021022_2</t>
+          <t>idp_NG021022_15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5085,7 +5232,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Birchi</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5095,31 +5242,36 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>idp_NG021022_7</t>
+          <t>idp_NG021022_2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5134,37 +5286,46 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kurfi B</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>idp_NG021022_7</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5179,23 +5340,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tsauri B</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_10</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>idp_NG021022_supp1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5203,13 +5368,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5224,23 +5394,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Birchi</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_11</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>idp_NG021022_supp2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5248,13 +5422,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5269,7 +5448,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Kurfi B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5279,27 +5458,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_12</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5314,7 +5498,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Birchi</t>
+          <t>Tsauri B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5324,27 +5508,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_13</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_10</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5359,7 +5548,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tsauri A</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5369,27 +5558,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_14</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_11</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5404,7 +5598,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Barkiya</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5414,27 +5608,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_15</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_12</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5449,7 +5648,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rawayau B</t>
+          <t>Birchi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5459,27 +5658,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_16</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_13</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5494,7 +5698,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tsauri B</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5504,27 +5708,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_3</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_14</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5539,7 +5748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tsauri A</t>
+          <t>Barkiya</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5549,27 +5758,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_5</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_15</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5584,7 +5798,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Rawayau B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5594,27 +5808,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_7</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_16</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5629,7 +5848,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kurfi A</t>
+          <t>Tsauri B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5639,27 +5858,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_9</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5684,27 +5908,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_supp1</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5719,7 +5948,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tsauri A</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5729,27 +5958,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_supp2</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_7</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5764,7 +5998,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kurfi B</t>
+          <t>Kurfi A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5774,27 +6008,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG021022_supp3</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_9</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5804,46 +6043,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>idp_NG021027_4</t>
+          <t>non_idp_NG021022_supp1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5853,46 +6093,47 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Karau</t>
+          <t>Tsauri A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>idp_NG021027_supp1</t>
+          <t>non_idp_NG021022_supp2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5902,12 +6143,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Kurfi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tamilo A</t>
+          <t>Kurfi B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5917,27 +6158,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_1</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021022_supp3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5952,23 +6198,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Doguru A</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_10</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>idp_NG021027_4</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5976,13 +6226,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6002,32 +6257,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_11</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>idp_NG021027_supp1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6042,7 +6306,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Tamilo A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6052,27 +6316,48 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_12</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6097,27 +6382,48 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_13</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_10</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6142,27 +6448,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_14</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_11</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6177,7 +6504,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Karau</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6187,27 +6514,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_15</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_12</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6222,7 +6554,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Doguru A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6232,27 +6564,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_16</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_13</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6267,7 +6604,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sonkaya</t>
+          <t>Karau</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6277,27 +6614,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_17</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_14</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6312,7 +6654,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Majigiri</t>
+          <t>Karau</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6322,27 +6664,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_2</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_15</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6357,7 +6704,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tamilo B</t>
+          <t>Gallu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6367,27 +6714,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_3</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_16</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6402,7 +6754,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gana Jigawa</t>
+          <t>Sonkaya</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6412,27 +6764,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_4</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_17</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6447,7 +6804,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bamle</t>
+          <t>Majigiri</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6457,27 +6814,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_5</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6492,7 +6854,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Tamilo B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6502,27 +6864,48 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_6</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_3</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6537,7 +6920,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tamilo A</t>
+          <t>Gana Jigawa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6547,27 +6930,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_8</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_4</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6582,7 +6970,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gana Jigawa</t>
+          <t>Bamle</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6592,45 +6980,232 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>non_idp_NG021027_9</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021027_5</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N61" s="10" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>non_idp_NG021027_6</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tamilo A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>non_idp_NG021027_8</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Gana Jigawa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>non_idp_NG021027_9</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6896,13 +7471,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1A1AD6-89D0-4B66-BDB6-2DDACA1BC08F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86F9826D-1026-4349-A974-74164E9CD860}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51B8C579-361F-4594-BFA2-22465B78F6B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C9860D2-9BA9-4D9C-A568-9F127A0F5249}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8F28A7-6F10-48F3-8C3F-1C4B9B8AF580}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B0794A-E268-40B2-B5F5-8AA4C805CCEB}"/>
 </file>